--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.58764523906207</v>
+        <v>3.182992351347587</v>
       </c>
       <c r="D2" t="n">
-        <v>14.56945228340329</v>
+        <v>2.367535996053035</v>
       </c>
       <c r="E2" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F2" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.34031170484064</v>
+        <v>4.117800652036604</v>
       </c>
       <c r="D3" t="n">
-        <v>7.248513780501445</v>
+        <v>1.177883489331485</v>
       </c>
       <c r="E3" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F3" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.05783245139938</v>
+        <v>4.5593977733524</v>
       </c>
       <c r="D4" t="n">
-        <v>19.54631044127694</v>
+        <v>3.176275446707503</v>
       </c>
       <c r="E4" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F4" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.957522734144664</v>
+        <v>1.455597444298508</v>
       </c>
       <c r="D5" t="n">
-        <v>13.68196952335806</v>
+        <v>2.223320047545686</v>
       </c>
       <c r="E5" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F5" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.385205252680206</v>
+        <v>1.200095853560533</v>
       </c>
       <c r="D6" t="n">
-        <v>11.44400231852645</v>
+        <v>1.859650376760548</v>
       </c>
       <c r="E6" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F6" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.95348410579805</v>
+        <v>3.079941167192184</v>
       </c>
       <c r="D7" t="n">
-        <v>3.840588571184251</v>
+        <v>0.6240956428174409</v>
       </c>
       <c r="E7" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F7" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.432294322049939</v>
+        <v>0.8827478273331152</v>
       </c>
       <c r="D8" t="n">
-        <v>11.1900638673352</v>
+        <v>1.818385378441969</v>
       </c>
       <c r="E8" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F8" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.36456721419021</v>
+        <v>1.68424217230591</v>
       </c>
       <c r="D9" t="n">
-        <v>9.237442259048985</v>
+        <v>1.50108436709546</v>
       </c>
       <c r="E9" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F9" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.69204620918609</v>
+        <v>3.849957508992739</v>
       </c>
       <c r="D10" t="n">
-        <v>9.748829991651272</v>
+        <v>1.584184873643332</v>
       </c>
       <c r="E10" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F10" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.49451123663352</v>
+        <v>3.330358075952948</v>
       </c>
       <c r="D11" t="n">
-        <v>13.14860772737563</v>
+        <v>2.13664875569854</v>
       </c>
       <c r="E11" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F11" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.68669585678665</v>
+        <v>3.68658807672783</v>
       </c>
       <c r="D12" t="n">
-        <v>7.229854463980942</v>
+        <v>1.174851350396903</v>
       </c>
       <c r="E12" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F12" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>78.13958667196681</v>
+        <v>12.69768283419461</v>
       </c>
       <c r="D13" t="n">
-        <v>64.70094225353105</v>
+        <v>10.5139031161988</v>
       </c>
       <c r="E13" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F13" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.077891137404028</v>
+        <v>1.150157309828155</v>
       </c>
       <c r="D14" t="n">
-        <v>34.76946623300655</v>
+        <v>5.650038262863565</v>
       </c>
       <c r="E14" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F14" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6.002508977591211</v>
+        <v>0.9754077088585719</v>
       </c>
       <c r="D15" t="n">
-        <v>38.93949906867029</v>
+        <v>6.327668598658923</v>
       </c>
       <c r="E15" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F15" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>44.88587162989951</v>
+        <v>7.293954139858671</v>
       </c>
       <c r="D16" t="n">
-        <v>33.45154228234495</v>
+        <v>5.435875620881055</v>
       </c>
       <c r="E16" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F16" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>20.74715509279391</v>
+        <v>3.371412702579011</v>
       </c>
       <c r="D17" t="n">
-        <v>49.77540925136544</v>
+        <v>8.088504003346884</v>
       </c>
       <c r="E17" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F17" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>78.38082970286315</v>
+        <v>12.73688482671526</v>
       </c>
       <c r="D18" t="n">
-        <v>65.92982910741836</v>
+        <v>10.71359722995548</v>
       </c>
       <c r="E18" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F18" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>14.11710811561026</v>
+        <v>2.294030068786667</v>
       </c>
       <c r="D19" t="n">
-        <v>51.2345341758126</v>
+        <v>8.325611803569547</v>
       </c>
       <c r="E19" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F19" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>74.04762416073497</v>
+        <v>12.03273892611943</v>
       </c>
       <c r="D20" t="n">
-        <v>45.28901130766157</v>
+        <v>7.359464337495006</v>
       </c>
       <c r="E20" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F20" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>50.44388982916507</v>
+        <v>8.197132097239324</v>
       </c>
       <c r="D21" t="n">
-        <v>28.64452791033654</v>
+        <v>4.654735785429688</v>
       </c>
       <c r="E21" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F21" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>52.80056625451154</v>
+        <v>8.580092016358126</v>
       </c>
       <c r="D22" t="n">
-        <v>22.5</v>
+        <v>3.65625</v>
       </c>
       <c r="E22" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F22" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>101.9752598967977</v>
+        <v>16.57097973322962</v>
       </c>
       <c r="D23" t="n">
-        <v>67.60691121804371</v>
+        <v>10.9861230729321</v>
       </c>
       <c r="E23" t="n">
-        <v>27.46811325850349</v>
+        <v>4.463568404506817</v>
       </c>
       <c r="F23" t="n">
-        <v>20.51092586053699</v>
+        <v>3.33302545233726</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
